--- a/Compititor's_Price/IKO_Prices/IKO_Prices_06-08-2025.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_06-08-2025.xlsx
@@ -555,17 +555,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£13.25</t>
+          <t>£12.95</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£13.25</t>
+          <t>£12.95</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£13.25</t>
+          <t>£12.95</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -612,17 +612,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£16.99</t>
+          <t>£16.54</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£16.99</t>
+          <t>£16.54</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£16.99</t>
+          <t>£16.54</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -669,17 +669,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£17.54</t>
+          <t>£17.33</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£17.54</t>
+          <t>£17.33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£17.54</t>
+          <t>£17.33</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -726,17 +726,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£22.13</t>
+          <t>£22.05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£22.13</t>
+          <t>£22.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£22.13</t>
+          <t>£22.05</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£27.83</t>
+          <t>£27.72</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£27.83</t>
+          <t>£27.72</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£27.83</t>
+          <t>£27.72</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£30.26</t>
+          <t>£30.24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£30.26</t>
+          <t>£30.24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£30.26</t>
+          <t>£30.24</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£30.44</t>
+          <t>£29.77</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£30.44</t>
+          <t>£29.77</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£30.44</t>
+          <t>£29.77</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1125,17 +1125,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£36.74</t>
+          <t>£36.65</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£36.74</t>
+          <t>£36.65</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£36.74</t>
+          <t>£36.65</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
